--- a/business_surveys/029_home_phone_fundraising_survey--business_surveys.xlsx
+++ b/business_surveys/029_home_phone_fundraising_survey--business_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -441,8 +441,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -525,7 +525,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>intro</t>
+          <t>Introduction</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -543,12 +543,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>contact_first_name</t>
+          <t>first_name</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>first_name</t>
+          <t>First Name</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -566,12 +566,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>contact_last_name</t>
+          <t>last_name</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>last_name</t>
+          <t>Last Name</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -594,7 +594,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -617,7 +617,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>Phone Number</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -640,7 +640,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>how_long</t>
+          <t>How Long</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -663,7 +663,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>frequency</t>
+          <t>Frequency</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -686,7 +686,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>concerns</t>
+          <t>Concerns</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -709,7 +709,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>comments</t>
+          <t>Comments</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -732,7 +732,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>assigned_tool</t>
+          <t>Assigned Tool</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -755,7 +755,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>output_file</t>
+          <t>Output File</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -778,7 +778,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>Category</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -801,7 +801,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>title</t>
+          <t>Title</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -824,7 +824,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>form_id</t>
+          <t>Form ID</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -842,18 +842,18 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>assigned_tool</t>
+          <t>assigned_tool_2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>assigned_tool</t>
+          <t>Assigned Tool 2</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -865,18 +865,18 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>output_file</t>
+          <t>output_file_2</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>output_file</t>
+          <t>Output File 2</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -893,13 +893,13 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>form_description</t>
+          <t>Form Description</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -916,13 +916,13 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>form_category</t>
+          <t>Form Category</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -939,13 +939,13 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>form_title</t>
+          <t>Form Title</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -962,13 +962,13 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>form_assigned_tool</t>
+          <t>Form Assigned Tool</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -985,13 +985,13 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>form_output_file</t>
+          <t>Form Output File</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -1003,18 +1003,18 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>form_description</t>
+          <t>form_description_2</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>form_description</t>
+          <t>Form Description 2</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -1026,18 +1026,18 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>form_category</t>
+          <t>form_category_2</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>form_category</t>
+          <t>Form Category 2</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -1049,18 +1049,18 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>form_title</t>
+          <t>form_title_2</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>form_title</t>
+          <t>Form Title 2</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -1072,18 +1072,18 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>form_assigned_tool</t>
+          <t>form_assigned_tool_2</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>form_assigned_tool</t>
+          <t>Form Assigned Tool 2</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -1102,8 +1102,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="38" customWidth="1" min="2" max="2"/>
+    <col width="38" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>concern1</t>
+          <t>i_am_concerned_about_data_security.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>concern1</t>
+          <t>I am concerned about data security.</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>concern2</t>
+          <t>i_am_concerned_about_data_privacy.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>concern2</t>
+          <t>I am concerned about data privacy.</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>concern3</t>
+          <t>i_am_concerned_about_data_accuracy.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>concern3</t>
+          <t>I am concerned about data accuracy.</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>concern4</t>
+          <t>i_am_concerned_about_data_integrity.</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>concern4</t>
+          <t>I am concerned about data integrity.</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>concern5</t>
+          <t>i_am_concerned_about_other</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>concern5</t>
+          <t>I am concerned about other</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>output_file1</t>
+          <t>file_1</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>output_file1</t>
+          <t>File 1</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>output_file2</t>
+          <t>file_2</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>output_file2</t>
+          <t>File 2</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>output_file3</t>
+          <t>file_3</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>output_file3</t>
+          <t>File 3</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>category1</t>
+          <t>category_1</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>category1</t>
+          <t>Category 1</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>category2</t>
+          <t>category_2</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>category2</t>
+          <t>Category 2</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>category3</t>
+          <t>category_3</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>category3</t>
+          <t>Category 3</t>
         </is>
       </c>
     </row>
